--- a/연도별 종합성적.xlsx
+++ b/연도별 종합성적.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C427286-FA64-43FA-BD69-71BB3B1FA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA34C027-1CD8-4269-9EC8-0CB17FDEFB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16354" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="7" xr2:uid="{B4FEA155-6799-4E2A-BB1B-501C30922FBE}"/>
+    <workbookView xWindow="16354" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{B4FEA155-6799-4E2A-BB1B-501C30922FBE}"/>
   </bookViews>
   <sheets>
     <sheet name="OB+두산" sheetId="10" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="238">
   <si>
     <t>연도</t>
   </si>
@@ -705,6 +705,63 @@
   </si>
   <si>
     <t>김시진,김성갑</t>
+  </si>
+  <si>
+    <t>이승엽,조성환</t>
+  </si>
+  <si>
+    <t>와카(0-2)</t>
+  </si>
+  <si>
+    <t>이승엽</t>
+  </si>
+  <si>
+    <t>와카(1-1),준플(2-1),플옵(2-0),한국(0-4)</t>
+  </si>
+  <si>
+    <t>준플(3-1),플옵(3-2),한국(4-1)</t>
+  </si>
+  <si>
+    <t>송일수</t>
+  </si>
+  <si>
+    <t>준플(3-2),플옵(3-1),한국(3-4)</t>
+  </si>
+  <si>
+    <t>김광수,김경문</t>
+  </si>
+  <si>
+    <t>준플(3-2),플옵(2-3)</t>
+  </si>
+  <si>
+    <t>플옵(4-2),한국(1-4)</t>
+  </si>
+  <si>
+    <t>플옵(3-0),한국(0-4)</t>
+  </si>
+  <si>
+    <t>준플(2-0),플옵(1-3)</t>
+  </si>
+  <si>
+    <t>준플(2-0),플옵(3-1),한국(4-2)</t>
+  </si>
+  <si>
+    <t>플옵(0-4)</t>
+  </si>
+  <si>
+    <t>윤동균,최주억</t>
+  </si>
+  <si>
+    <t>윤동균</t>
+  </si>
+  <si>
+    <t>이재우,윤동균</t>
+  </si>
+  <si>
+    <t>이광환,이재우</t>
+  </si>
+  <si>
+    <t>김성근,강태정</t>
   </si>
 </sst>
 </file>
@@ -1125,25 +1182,25 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0.61499999999999999</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -1151,28 +1208,25 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>144</v>
       </c>
       <c r="D3">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="G3">
-        <v>0.60299999999999998</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
+        <v>0.442</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -1180,28 +1234,28 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>144</v>
       </c>
       <c r="D4">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G4">
-        <v>0.53500000000000003</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>220</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
@@ -1209,28 +1263,28 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>144</v>
       </c>
       <c r="D5">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G5">
-        <v>0.60599999999999998</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
@@ -1238,28 +1292,25 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>144</v>
       </c>
       <c r="D6">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="G6">
-        <v>0.61299999999999999</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
@@ -1267,28 +1318,28 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>144</v>
       </c>
       <c r="D7">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>0.55400000000000005</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -1296,7 +1347,7 @@
         <v>21</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>144</v>
@@ -1314,10 +1365,10 @@
         <v>0.56399999999999995</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -1325,28 +1376,28 @@
         <v>24</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>144</v>
       </c>
       <c r="D9">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G9">
-        <v>0.55200000000000005</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -1354,25 +1405,28 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10">
         <v>144</v>
       </c>
       <c r="D10">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="G10">
-        <v>0.47599999999999998</v>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="H10" t="s">
+        <v>109</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -1380,25 +1434,28 @@
         <v>27</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C11">
         <v>144</v>
       </c>
       <c r="D11">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G11">
-        <v>0.48899999999999999</v>
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="H11" t="s">
+        <v>95</v>
       </c>
       <c r="I11" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -1406,28 +1463,28 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>144</v>
       </c>
       <c r="D12">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="G12">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="I12" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -1435,25 +1492,28 @@
         <v>31</v>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>144</v>
       </c>
       <c r="D13">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G13">
-        <v>0.45100000000000001</v>
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="H13" t="s">
+        <v>223</v>
       </c>
       <c r="I13" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -1461,28 +1521,25 @@
         <v>32</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>128</v>
       </c>
       <c r="D14">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G14">
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="H14" t="s">
-        <v>33</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="I14" t="s">
-        <v>34</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -1490,28 +1547,28 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
         <v>128</v>
       </c>
       <c r="D15">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>54</v>
       </c>
       <c r="G15">
-        <v>0.57799999999999996</v>
+        <v>0.56799999999999995</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>225</v>
       </c>
       <c r="I15" t="s">
-        <v>36</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
@@ -1519,25 +1576,28 @@
         <v>37</v>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>133</v>
       </c>
       <c r="D16">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G16">
-        <v>0.442</v>
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="H16" t="s">
+        <v>140</v>
       </c>
       <c r="I16" t="s">
-        <v>36</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
@@ -1545,25 +1605,25 @@
         <v>38</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>133</v>
       </c>
       <c r="D17">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G17">
-        <v>0.45</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="I17" t="s">
-        <v>39</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
@@ -1571,25 +1631,28 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>133</v>
       </c>
       <c r="D18">
+        <v>73</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18">
         <v>57</v>
       </c>
-      <c r="E18">
-        <v>5</v>
-      </c>
-      <c r="F18">
-        <v>71</v>
-      </c>
       <c r="G18">
-        <v>0.44500000000000001</v>
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="H18" t="s">
+        <v>227</v>
       </c>
       <c r="I18" t="s">
-        <v>39</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
@@ -1597,25 +1660,28 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C19">
         <v>133</v>
       </c>
       <c r="D19">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G19">
-        <v>0.41899999999999998</v>
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="H19" t="s">
+        <v>136</v>
       </c>
       <c r="I19" t="s">
-        <v>42</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
@@ -1623,25 +1689,28 @@
         <v>43</v>
       </c>
       <c r="B20">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>126</v>
       </c>
       <c r="D20">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="G20">
-        <v>0.36499999999999999</v>
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="H20" t="s">
+        <v>228</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
@@ -1649,25 +1718,28 @@
         <v>44</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>126</v>
       </c>
       <c r="D21">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G21">
-        <v>0.48299999999999998</v>
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="H21" t="s">
+        <v>197</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
@@ -1675,25 +1747,25 @@
         <v>45</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>126</v>
       </c>
       <c r="D22">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G22">
-        <v>0.38500000000000001</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
@@ -1701,25 +1773,28 @@
         <v>47</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>126</v>
       </c>
       <c r="D23">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="G23">
-        <v>0.432</v>
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="H23" t="s">
+        <v>229</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
@@ -1727,25 +1802,28 @@
         <v>49</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C24">
         <v>133</v>
       </c>
       <c r="D24">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G24">
-        <v>0.45700000000000002</v>
+        <v>0.53</v>
+      </c>
+      <c r="H24" t="s">
+        <v>230</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
@@ -1753,25 +1831,25 @@
         <v>50</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>133</v>
       </c>
       <c r="D25">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
       <c r="F25">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G25">
-        <v>0.45800000000000002</v>
+        <v>0.435</v>
       </c>
       <c r="I25" t="s">
-        <v>51</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
@@ -1779,7 +1857,7 @@
         <v>52</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>133</v>
@@ -1788,19 +1866,16 @@
         <v>66</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G26">
-        <v>0.52</v>
-      </c>
-      <c r="H26" t="s">
-        <v>53</v>
+        <v>0.504</v>
       </c>
       <c r="I26" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
@@ -1808,25 +1883,28 @@
         <v>55</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <v>133</v>
       </c>
       <c r="D27">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G27">
-        <v>0.46400000000000002</v>
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="H27" t="s">
+        <v>231</v>
       </c>
       <c r="I27" t="s">
-        <v>56</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
@@ -1834,28 +1912,28 @@
         <v>57</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>133</v>
       </c>
       <c r="D28">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G28">
-        <v>0.51500000000000001</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="I28" t="s">
-        <v>59</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
@@ -1863,25 +1941,28 @@
         <v>60</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C29">
         <v>132</v>
       </c>
       <c r="D29">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="G29">
-        <v>0.46600000000000003</v>
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="H29" t="s">
+        <v>232</v>
       </c>
       <c r="I29" t="s">
-        <v>61</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
@@ -1889,28 +1970,28 @@
         <v>62</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <v>126</v>
       </c>
       <c r="D30">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30">
         <v>62</v>
       </c>
       <c r="G30">
-        <v>0.504</v>
+        <v>0.496</v>
       </c>
       <c r="H30" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="I30" t="s">
-        <v>61</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
@@ -1918,28 +1999,25 @@
         <v>64</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>126</v>
       </c>
       <c r="D31">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F31">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="G31">
-        <v>0.58899999999999997</v>
-      </c>
-      <c r="H31" t="s">
-        <v>65</v>
+        <v>0.47099999999999997</v>
       </c>
       <c r="I31" t="s">
-        <v>61</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
@@ -1947,25 +2025,25 @@
         <v>66</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <v>126</v>
       </c>
       <c r="D32">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G32">
-        <v>0.41299999999999998</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="I32" t="s">
-        <v>67</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
@@ -1973,7 +2051,7 @@
         <v>68</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33">
         <v>126</v>
@@ -1982,19 +2060,19 @@
         <v>74</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G33">
-        <v>0.60699999999999998</v>
+        <v>0.61199999999999999</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="I33" t="s">
-        <v>51</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
@@ -2002,28 +2080,25 @@
         <v>69</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C34">
         <v>126</v>
       </c>
       <c r="D34">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G34">
-        <v>0.64300000000000002</v>
-      </c>
-      <c r="H34" t="s">
-        <v>70</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="I34" t="s">
-        <v>51</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
@@ -2031,7 +2106,7 @@
         <v>71</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C35">
         <v>126</v>
@@ -2040,19 +2115,19 @@
         <v>66</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F35">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G35">
-        <v>0.53700000000000003</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
@@ -2060,25 +2135,25 @@
         <v>73</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>126</v>
       </c>
       <c r="D36">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G36">
-        <v>0.43099999999999999</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
@@ -2086,25 +2161,25 @@
         <v>74</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C37">
         <v>126</v>
       </c>
       <c r="D37">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G37">
-        <v>0.42399999999999999</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="I37" t="s">
-        <v>75</v>
+        <v>235</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
@@ -2112,28 +2187,25 @@
         <v>76</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C38">
         <v>120</v>
       </c>
       <c r="D38">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F38">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="G38">
-        <v>0.59199999999999997</v>
-      </c>
-      <c r="H38" t="s">
-        <v>70</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="I38" t="s">
-        <v>75</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
@@ -2141,25 +2213,25 @@
         <v>77</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>120</v>
       </c>
       <c r="D39">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G39">
-        <v>0.42199999999999999</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="I39" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
@@ -2167,25 +2239,25 @@
         <v>79</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>108</v>
       </c>
       <c r="D40">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G40">
-        <v>0.38500000000000001</v>
+        <v>0.50900000000000001</v>
       </c>
       <c r="I40" t="s">
-        <v>80</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
@@ -2193,25 +2265,28 @@
         <v>81</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C41">
         <v>108</v>
       </c>
       <c r="D41">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E41">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G41">
-        <v>0.495</v>
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="H41" t="s">
+        <v>138</v>
       </c>
       <c r="I41" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
@@ -2219,25 +2294,28 @@
         <v>83</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42">
         <v>108</v>
       </c>
       <c r="D42">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E42">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F42">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G42">
-        <v>0.59</v>
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="H42" t="s">
+        <v>138</v>
       </c>
       <c r="I42" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
@@ -2245,25 +2323,25 @@
         <v>85</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>110</v>
       </c>
       <c r="D43">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G43">
-        <v>0.40400000000000003</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="I43" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
@@ -2271,25 +2349,25 @@
         <v>87</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44">
         <v>100</v>
       </c>
       <c r="D44">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G44">
-        <v>0.51500000000000001</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="I44" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
@@ -2297,28 +2375,25 @@
         <v>89</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C45">
         <v>100</v>
       </c>
       <c r="D45">
+        <v>44</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
         <v>55</v>
       </c>
-      <c r="E45">
-        <v>2</v>
-      </c>
-      <c r="F45">
-        <v>43</v>
-      </c>
       <c r="G45">
-        <v>0.56100000000000005</v>
-      </c>
-      <c r="H45" t="s">
-        <v>90</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="I45" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
@@ -2326,25 +2401,28 @@
         <v>92</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46">
         <v>80</v>
       </c>
       <c r="D46">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G46">
-        <v>0.57499999999999996</v>
+        <v>0.7</v>
+      </c>
+      <c r="H46" t="s">
+        <v>12</v>
       </c>
       <c r="I46" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
